--- a/bot/src/data/table1.xlsx
+++ b/bot/src/data/table1.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Новая папка\hackathonMiran\bot\src\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DE60140C-8640-4201-911C-3CCB005E517B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{420B3218-E2C2-4372-9733-AB2B2BA6ECAC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="14616" xr2:uid="{722ABB53-3B03-4FE4-955B-D2E70769122A}"/>
   </bookViews>
@@ -937,9 +937,7 @@
       <c r="B4" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="C4" s="5">
-        <v>1</v>
-      </c>
+      <c r="C4" s="5"/>
       <c r="D4" s="5"/>
       <c r="E4" s="6"/>
     </row>
@@ -951,9 +949,7 @@
         <v>35</v>
       </c>
       <c r="C5" s="48"/>
-      <c r="D5" s="48">
-        <v>0</v>
-      </c>
+      <c r="D5" s="48"/>
       <c r="E5" s="46"/>
     </row>
     <row r="6" spans="1:5" ht="97.8" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
@@ -970,9 +966,7 @@
       <c r="B7" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="C7" s="5">
-        <v>1</v>
-      </c>
+      <c r="C7" s="5"/>
       <c r="D7" s="5"/>
       <c r="E7" s="8"/>
     </row>
@@ -983,9 +977,7 @@
       <c r="B8" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="C8" s="5">
-        <v>1</v>
-      </c>
+      <c r="C8" s="5"/>
       <c r="D8" s="5"/>
       <c r="E8" s="8"/>
     </row>
@@ -996,9 +988,7 @@
       <c r="B9" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="C9" s="5">
-        <v>1</v>
-      </c>
+      <c r="C9" s="5"/>
       <c r="D9" s="5"/>
       <c r="E9" s="8"/>
     </row>
@@ -1010,9 +1000,7 @@
         <v>12</v>
       </c>
       <c r="C10" s="5"/>
-      <c r="D10" s="5">
-        <v>0</v>
-      </c>
+      <c r="D10" s="5"/>
       <c r="E10" s="8"/>
     </row>
     <row r="11" spans="1:5" ht="33.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
@@ -1022,7 +1010,7 @@
       </c>
       <c r="C11" s="11">
         <f>SUM(C4:C10)</f>
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="D11" s="12"/>
       <c r="E11" s="12"/>
@@ -1056,9 +1044,7 @@
       <c r="B14" s="30" t="s">
         <v>36</v>
       </c>
-      <c r="C14" s="31">
-        <v>1</v>
-      </c>
+      <c r="C14" s="31"/>
       <c r="D14" s="31"/>
       <c r="E14" s="29"/>
     </row>
@@ -1070,9 +1056,7 @@
         <v>37</v>
       </c>
       <c r="C15" s="32"/>
-      <c r="D15" s="32">
-        <v>0</v>
-      </c>
+      <c r="D15" s="32"/>
       <c r="E15" s="32"/>
     </row>
     <row r="16" spans="1:5" ht="150" customHeight="1" x14ac:dyDescent="0.3">
@@ -1093,9 +1077,7 @@
       <c r="B17" s="19" t="s">
         <v>18</v>
       </c>
-      <c r="C17" s="5">
-        <v>1</v>
-      </c>
+      <c r="C17" s="5"/>
       <c r="D17" s="5"/>
       <c r="E17" s="8"/>
     </row>
@@ -1106,9 +1088,7 @@
       <c r="B18" s="30" t="s">
         <v>39</v>
       </c>
-      <c r="C18" s="31">
-        <v>1</v>
-      </c>
+      <c r="C18" s="31"/>
       <c r="D18" s="31"/>
       <c r="E18" s="32"/>
     </row>
@@ -1120,9 +1100,7 @@
         <v>45</v>
       </c>
       <c r="C19" s="32"/>
-      <c r="D19" s="32">
-        <v>0</v>
-      </c>
+      <c r="D19" s="32"/>
       <c r="E19" s="32"/>
     </row>
     <row r="20" spans="1:5" ht="33.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
@@ -1132,7 +1110,7 @@
       </c>
       <c r="C20" s="11">
         <f>SUM(C14:C19)</f>
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="D20" s="12"/>
       <c r="E20" s="12"/>
@@ -1155,9 +1133,7 @@
       <c r="B22" s="4" t="s">
         <v>22</v>
       </c>
-      <c r="C22" s="5">
-        <v>1</v>
-      </c>
+      <c r="C22" s="5"/>
       <c r="D22" s="5"/>
       <c r="E22" s="8"/>
     </row>
@@ -1168,9 +1144,7 @@
       <c r="B23" s="30" t="s">
         <v>40</v>
       </c>
-      <c r="C23" s="31">
-        <v>1</v>
-      </c>
+      <c r="C23" s="31"/>
       <c r="D23" s="31"/>
       <c r="E23" s="32"/>
     </row>
@@ -1181,9 +1155,7 @@
       <c r="B24" s="4" t="s">
         <v>23</v>
       </c>
-      <c r="C24" s="5">
-        <v>1</v>
-      </c>
+      <c r="C24" s="5"/>
       <c r="D24" s="5"/>
       <c r="E24" s="8"/>
     </row>
@@ -1194,9 +1166,7 @@
       <c r="B25" s="4" t="s">
         <v>24</v>
       </c>
-      <c r="C25" s="5">
-        <v>1</v>
-      </c>
+      <c r="C25" s="5"/>
       <c r="D25" s="5"/>
       <c r="E25" s="8"/>
     </row>
@@ -1207,9 +1177,7 @@
       <c r="B26" s="4" t="s">
         <v>25</v>
       </c>
-      <c r="C26" s="5">
-        <v>1</v>
-      </c>
+      <c r="C26" s="5"/>
       <c r="D26" s="5"/>
       <c r="E26" s="8"/>
     </row>
@@ -1220,9 +1188,7 @@
       <c r="B27" s="30" t="s">
         <v>41</v>
       </c>
-      <c r="C27" s="31">
-        <v>1</v>
-      </c>
+      <c r="C27" s="31"/>
       <c r="D27" s="31"/>
       <c r="E27" s="32"/>
     </row>
@@ -1233,7 +1199,7 @@
       </c>
       <c r="C28" s="11">
         <f>SUM(C22:C27)</f>
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="D28" s="11"/>
       <c r="E28" s="12"/>
@@ -1294,9 +1260,7 @@
       <c r="B34" s="30" t="s">
         <v>42</v>
       </c>
-      <c r="C34" s="28">
-        <v>1</v>
-      </c>
+      <c r="C34" s="28"/>
       <c r="D34" s="28"/>
       <c r="E34" s="29"/>
     </row>
@@ -1307,9 +1271,7 @@
       <c r="B35" s="33" t="s">
         <v>43</v>
       </c>
-      <c r="C35" s="28">
-        <v>1</v>
-      </c>
+      <c r="C35" s="28"/>
       <c r="D35" s="28"/>
       <c r="E35" s="29"/>
     </row>
@@ -1320,9 +1282,7 @@
       <c r="B36" s="33" t="s">
         <v>44</v>
       </c>
-      <c r="C36" s="28">
-        <v>1</v>
-      </c>
+      <c r="C36" s="28"/>
       <c r="D36" s="28"/>
       <c r="E36" s="29"/>
     </row>
@@ -1333,9 +1293,7 @@
       <c r="B37" s="24" t="s">
         <v>30</v>
       </c>
-      <c r="C37" s="25">
-        <v>1</v>
-      </c>
+      <c r="C37" s="25"/>
       <c r="D37" s="25"/>
       <c r="E37" s="6"/>
     </row>
@@ -1346,9 +1304,7 @@
       <c r="B38" s="4" t="s">
         <v>31</v>
       </c>
-      <c r="C38" s="25">
-        <v>1</v>
-      </c>
+      <c r="C38" s="25"/>
       <c r="D38" s="25"/>
       <c r="E38" s="6"/>
     </row>
@@ -1359,9 +1315,7 @@
       <c r="B39" s="4" t="s">
         <v>32</v>
       </c>
-      <c r="C39" s="25">
-        <v>1</v>
-      </c>
+      <c r="C39" s="25"/>
       <c r="D39" s="25"/>
       <c r="E39" s="6"/>
     </row>
@@ -1372,7 +1326,7 @@
       </c>
       <c r="C40" s="11">
         <f>SUM(C34:C39)</f>
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="D40" s="11"/>
       <c r="E40" s="12"/>
@@ -1384,7 +1338,7 @@
       </c>
       <c r="C41" s="11">
         <f>($C$11+$C$20+$C$28+$C$40)/4</f>
-        <v>4.75</v>
+        <v>0</v>
       </c>
       <c r="D41" s="11"/>
       <c r="E41" s="12"/>
